--- a/Result/profitability/1536.xlsx
+++ b/Result/profitability/1536.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3700000000000001</v>
+        <v>-0.40625</v>
       </c>
       <c r="N2" t="n">
-        <v>8.24</v>
+        <v>7.66875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.63</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.25375</v>
+        <v>-0.365</v>
       </c>
       <c r="N3" t="n">
-        <v>10.1525</v>
+        <v>10.4275</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.21</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.265</v>
+        <v>-0.2925</v>
       </c>
       <c r="N4" t="n">
-        <v>12.4775</v>
+        <v>12.47</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-2.51</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5325</v>
+        <v>-0.41375</v>
       </c>
       <c r="N5" t="n">
-        <v>11.87375</v>
+        <v>12.22125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.49</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.40125</v>
+        <v>-0.4562499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>13.39</v>
+        <v>13.745</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-6.47</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.19125</v>
+        <v>-1.18</v>
       </c>
       <c r="N7" t="n">
-        <v>13.19125</v>
+        <v>14.52</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.51</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.17</v>
+        <v>-1.17875</v>
       </c>
       <c r="N8" t="n">
-        <v>17.1775</v>
+        <v>17.22125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>-0.17</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.89375</v>
+        <v>-0.8937499999999999</v>
       </c>
       <c r="N13" t="n">
         <v>19.42875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1536</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1162</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1082</v>
+      </c>
+      <c r="E75" t="n">
+        <v>80</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-123</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-10.60%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-53</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-176</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-164</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.48125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5.09875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.06999999999999995</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1346153846153846</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.3500000000000005</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.05368098159509205</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6168831168831169</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.6797066014669928</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
